--- a/artfynd/A 24108-2024 artfynd.xlsx
+++ b/artfynd/A 24108-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,68 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57714724</v>
+        <v>69538118</v>
       </c>
       <c r="B2" t="n">
-        <v>9491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101479</v>
+        <v>5445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585535.7646775021</v>
+        <v>585243</v>
       </c>
       <c r="R2" t="n">
-        <v>6310793.093119159</v>
+        <v>6310838</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,24 +743,14 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmars trädinventering, Observatör Karin Arnell</t>
+          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Jerry Svensson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,11 +762,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>skogsek</t>
@@ -807,30 +772,20 @@
           <t>Quercus robur</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Omkrets 215</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Levande (5a) # Quercus robur # Omkrets 215</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>112554</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Jonas Hedin</t>
+          <t>Via Thomas Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -841,68 +796,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>57714431</v>
+        <v>69538121</v>
       </c>
       <c r="B3" t="n">
-        <v>9491</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101479</v>
+        <v>5445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585513.0951940126</v>
+        <v>585349</v>
       </c>
       <c r="R3" t="n">
-        <v>6310805.179478955</v>
+        <v>6310842</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -929,24 +864,14 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmars trädinventering, Observatör Karin Arnell</t>
+          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Jerry Svensson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -958,11 +883,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>skogsek</t>
@@ -973,30 +893,20 @@
           <t>Quercus robur</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Omkrets 320</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Dött stående (5a) # Quercus robur # Omkrets 320</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>113379</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Jonas Hedin</t>
+          <t>Via Thomas Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1007,68 +917,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>57714284</v>
+        <v>69538123</v>
       </c>
       <c r="B4" t="n">
-        <v>9491</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101479</v>
+        <v>5445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585603.733315145</v>
+        <v>585483</v>
       </c>
       <c r="R4" t="n">
-        <v>6310811.955556331</v>
+        <v>6310799</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1095,24 +985,14 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmars trädinventering, Observatör Karin Arnell</t>
+          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Karin Arnell</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1124,11 +1004,6 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>skogsek</t>
@@ -1139,30 +1014,20 @@
           <t>Quercus robur</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Omkrets 253</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Dött stående (5a) # Quercus robur # Omkrets 253</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>112494</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Jonas Hedin</t>
+          <t>Via Thomas Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1173,68 +1038,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57714287</v>
+        <v>69538125</v>
       </c>
       <c r="B5" t="n">
-        <v>9491</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101479</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585438.7858596337</v>
+        <v>585565</v>
       </c>
       <c r="R5" t="n">
-        <v>6310828.757304646</v>
+        <v>6310804</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1261,24 +1106,14 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmars trädinventering, Observatör Jerry Svensson</t>
+          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Karin Arnell</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1290,11 +1125,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>skogsek</t>
@@ -1305,30 +1135,20 @@
           <t>Quercus robur</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Omkrets 356</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Levande (6a) # Quercus robur # Omkrets 356</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>113374</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Jonas Hedin</t>
+          <t>Via Thomas Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1339,37 +1159,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69538118</v>
+        <v>69531318</v>
       </c>
       <c r="B6" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5445</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1379,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585242.8281447362</v>
+        <v>585576</v>
       </c>
       <c r="R6" t="n">
-        <v>6310837.835093206</v>
+        <v>6310788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1412,24 +1227,14 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Jerry Svensson</t>
+          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Karin Arnell</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1475,37 +1280,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69538123</v>
+        <v>69531319</v>
       </c>
       <c r="B7" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5445</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1515,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585483.1431156376</v>
+        <v>585565</v>
       </c>
       <c r="R7" t="n">
-        <v>6310799.106276466</v>
+        <v>6310804</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1548,19 +1348,9 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2007-01-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1611,15 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69531319</v>
+        <v>69531322</v>
       </c>
       <c r="B8" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1651,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585565.0691191196</v>
+        <v>585493</v>
       </c>
       <c r="R8" t="n">
-        <v>6310804.065213792</v>
+        <v>6310807</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1684,19 +1469,9 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2007-01-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1747,37 +1522,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69538121</v>
+        <v>69531323</v>
       </c>
       <c r="B9" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5445</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1787,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585348.8270371531</v>
+        <v>585483</v>
       </c>
       <c r="R9" t="n">
-        <v>6310842.19163641</v>
+        <v>6310799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1820,24 +1590,14 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Jerry Svensson</t>
+          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Karin Arnell</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1883,37 +1643,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69538125</v>
+        <v>69531325</v>
       </c>
       <c r="B10" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5445</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1923,10 +1678,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585565.0691191196</v>
+        <v>585426</v>
       </c>
       <c r="R10" t="n">
-        <v>6310804.065213792</v>
+        <v>6310832</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1956,24 +1711,14 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Karin Arnell</t>
+          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Jerry Svensson</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2019,53 +1764,63 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>69531322</v>
+        <v>57714283</v>
       </c>
       <c r="B11" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9596</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>101479</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585492.8253499889</v>
+        <v>585628</v>
       </c>
       <c r="R11" t="n">
-        <v>6310806.945865161</v>
+        <v>6310804</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2092,24 +1847,14 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Karin Arnell</t>
+          <t>Länsstyrelsen i Kalmars trädinventering, Observatör Karin Arnell</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2121,6 +1866,11 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>skogsek</t>
@@ -2131,20 +1881,30 @@
           <t>Quercus robur</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Omkrets 312</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Levande (5a) # Quercus robur # Omkrets 312</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>112487</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Thomas Johansson</t>
+          <t>Via Jonas Hedin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2155,53 +1915,63 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>69531325</v>
+        <v>57714284</v>
       </c>
       <c r="B12" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9596</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>101479</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585426.1464188661</v>
+        <v>585604</v>
       </c>
       <c r="R12" t="n">
-        <v>6310831.772237498</v>
+        <v>6310812</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2228,24 +1998,14 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Jerry Svensson</t>
+          <t>Länsstyrelsen i Kalmars trädinventering, Observatör Karin Arnell</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2257,6 +2017,11 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>skogsek</t>
@@ -2267,20 +2032,30 @@
           <t>Quercus robur</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Omkrets 253</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Dött stående (5a) # Quercus robur # Omkrets 253</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>112494</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Thomas Johansson</t>
+          <t>Via Jonas Hedin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2291,53 +2066,63 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>69531318</v>
+        <v>57714285</v>
       </c>
       <c r="B13" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6439</v>
+        <v>101479</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585575.7916134928</v>
+        <v>585536</v>
       </c>
       <c r="R13" t="n">
-        <v>6310787.913012829</v>
+        <v>6310793</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2364,24 +2149,14 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Karin Arnell</t>
+          <t>Länsstyrelsen i Kalmars trädinventering, Observatör Karin Arnell</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2393,6 +2168,11 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>skogsek</t>
@@ -2403,20 +2183,30 @@
           <t>Quercus robur</t>
         </is>
       </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Omkrets 215</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Levande (5a) # Quercus robur # Omkrets 215</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>112554</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Thomas Johansson</t>
+          <t>Via Jonas Hedin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2427,53 +2217,63 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>69531323</v>
+        <v>57714287</v>
       </c>
       <c r="B14" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>101479</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585483.1431156376</v>
+        <v>585439</v>
       </c>
       <c r="R14" t="n">
-        <v>6310799.106276466</v>
+        <v>6310829</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2500,24 +2300,14 @@
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2007-01-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Karin Arnell</t>
+          <t>Länsstyrelsen i Kalmars trädinventering, Observatör Jerry Svensson</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2529,6 +2319,11 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>skogsek</t>
@@ -2539,23 +2334,184 @@
           <t>Quercus robur</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Omkrets 356</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Levande (6a) # Quercus robur # Omkrets 356</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>113374</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Thomas Johansson</t>
+          <t>Via Jonas Hedin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trädinventeringen i Kalmar län</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>57714288</v>
+      </c>
+      <c r="B15" t="n">
+        <v>9596</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101479</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Läderbagge</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Osmoderma eremita</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalmar län (lokalnamn saknas), Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>585513</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6310805</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2007-01-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2007-01-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Kalmars trädinventering, Observatör Karin Arnell</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Omkrets 320</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Dött stående (5a) # Quercus robur # Omkrets 320</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>113379</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Trädinventeringen i Kalmar län</t>
         </is>

--- a/artfynd/A 24108-2024 artfynd.xlsx
+++ b/artfynd/A 24108-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538121</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538125</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531318</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1398,6 +1428,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531319</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1519,6 +1554,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531322</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1640,6 +1680,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531323</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1761,6 +1806,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531325</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1912,6 +1962,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714283</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2063,6 +2118,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714284</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2214,6 +2274,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714285</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2365,6 +2430,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714287</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2516,8 +2586,29 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714288</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>